--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (March 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2139,7 +2139,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2757,71 +2757,71 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01131</t>
+          <t>CM-26-01206</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Aalto Blanco</t>
+          <t>Beau-Séjour Bécot</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Château Beau-Séjour Bécot</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>769</v>
+        <v>2858</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>4'359.83</t>
+          <t>23'820.78</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0187</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0054</v>
+        <v>0.0295</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01206</t>
+          <t>CM-26-01160</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2831,537 +2831,537 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Beau-Séjour Bécot</t>
+          <t>Châteauneuf du Pape</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Beau-Séjour Bécot</t>
+          <t>Clos des Papes</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2858</v>
+        <v>1631</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>23'820.78</t>
+          <t>15'338.87</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0237</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.019</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>756</v>
+        <v>860</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01160</t>
+          <t>CM-26-01151</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape</t>
+          <t>Champagne Brut Dom Pérignon</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Clos des Papes</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1631</v>
+        <v>984</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>15'338.87</t>
+          <t>12'917.47</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0237</v>
+        <v>0.0174</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>860</v>
+        <v>906</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01151</t>
+          <t>CM-26-01190</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Dom Pérignon</t>
+          <t>Garrus Rosé</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Château d'Esclans</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>984</v>
+        <v>3376</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>12'917.47</t>
+          <t>12'745.67</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0174</v>
+        <v>0.0134</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.016</v>
+        <v>0.0158</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0168</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01190</t>
+          <t>CM-26-01166</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Garrus Rosé</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château d'Esclans</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3376</v>
+        <v>457</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>12'745.67</t>
+          <t>8'709.95</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0134</v>
+        <v>0.0142</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0158</v>
+        <v>0.0108</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0144</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01166</t>
+          <t>CM-26-01161</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Brunello di Montalcino Riserva</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Biondi Santi</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>457</v>
+        <v>1180</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>8'709.95</t>
+          <t>13'542.92</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0073</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0108</v>
+        <v>0.0168</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0128</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>948</v>
+        <v>992</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01161</t>
+          <t>CM-26-01188</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Riserva</t>
+          <t>Cepparello</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Biondi Santi</t>
+          <t>Isole e Olena</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1180</v>
+        <v>2808</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>13'542.92</t>
+          <t>5'370.64</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.0067</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0111</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>992</v>
+        <v>1009</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01188</t>
+          <t>CM-26-01196</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Cepparello</t>
+          <t>Trotanoy</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Isole e Olena</t>
+          <t>Château Trotanoy</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2808</v>
+        <v>1349</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>5'370.64</t>
+          <t>6'553.48</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0047</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0081</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0077</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01196</t>
+          <t>CM-26-01165</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Pavillon Blanc Second Vin</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Trotanoy</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1349</v>
+        <v>3510</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>6'553.48</t>
+          <t>4'412.30</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0047</v>
+        <v>0.0043</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0081</v>
+        <v>0.0055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0061</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1019</v>
+        <v>1121</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01165</t>
+          <t>CM-26-01179</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc Second Vin</t>
+          <t>La Malvasia di Milano</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>La Vigna di Leonardo</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3510</v>
+        <v>359</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>4'412.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01179</t>
+          <t>CM-26-01203</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3371,26 +3371,26 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>La Malvasia di Milano</t>
+          <t>Chambertin</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>La Vigna di Leonardo</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3417,11 +3417,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01203</t>
+          <t>CM-26-01208</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3477,11 +3477,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01208</t>
+          <t>CM-26-01209</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3537,11 +3537,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01209</t>
+          <t>CM-26-01211</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Chambertin</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -3595,68 +3595,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>1125</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01211</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Armand Rousseau</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>107</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N27"/>
+  <autoFilter ref="A3:N26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3700,7 +3640,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5261,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -6179,131 +6119,131 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00966</t>
+          <t>CM-26-01022</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Dom Pérignon Rosé</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1195</v>
+        <v>566</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>57'068.01</t>
+          <t>65'929.06</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0396</v>
+        <v>0.0267</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0708</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0521</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01022</t>
+          <t>CM-26-01066</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Galatrona</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Fattoria Petrolo</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>566</v>
+        <v>2984</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>65'929.06</t>
+          <t>46'947.63</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0267</v>
+        <v>0.0418</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01066</t>
+          <t>CM-26-01026</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6313,7 +6253,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Galatrona</t>
+          <t>Corton</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -6323,47 +6263,47 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Domaine Rapet Père &amp; Fils</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2984</v>
+        <v>3194</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>46'947.63</t>
+          <t>44'534.60</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.037</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0582</v>
+        <v>0.0552</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00971</t>
+          <t>CM-26-01097</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6373,67 +6313,67 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Barolo Monfortino Riserva</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Giacomo Conterno</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>976</v>
+        <v>585</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>72'489.59</t>
+          <t>57'108.49</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.0258</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0453</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01026</t>
+          <t>CM-26-01146</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Corton</t>
+          <t>Echezeaux</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -6443,47 +6383,47 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Rapet Père &amp; Fils</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3194</v>
+        <v>1652</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>44'534.60</t>
+          <t>51'694.28</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0274</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0552</v>
+        <v>0.0641</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0443</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01097</t>
+          <t>CM-26-01104</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -6493,17 +6433,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Harlan Estate</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -6512,38 +6452,38 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>585</v>
+        <v>669</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>57'108.49</t>
+          <t>60'905.73</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0194</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0755</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0438</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01146</t>
+          <t>CM-26-01150</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -6553,29 +6493,29 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Echezeaux</t>
+          <t>Lynch Bages</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Lynch Bages</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1652</v>
+        <v>1896</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -6584,86 +6524,86 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>51'694.28</t>
+          <t>49'549.21</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
         <v>0.0274</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0641</v>
+        <v>0.0614</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0421</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01104</t>
+          <t>CM-26-01090</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Blanc de Blancs Dosaggio Zero</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Harlan Estate</t>
+          <t>Azienda Agricola Alessandra Divella</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>669</v>
+        <v>2344</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>60'905.73</t>
+          <t>26'400.15</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0194</v>
+        <v>0.045</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0755</v>
+        <v>0.0327</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01150</t>
+          <t>CM-26-01113</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -6673,7 +6613,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Lynch Bages</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -6683,47 +6623,47 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Lynch Bages</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1896</v>
+        <v>2206</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>49'549.21</t>
+          <t>48'374.15</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0274</v>
+        <v>0.0254</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0614</v>
+        <v>0.06</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.041</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01090</t>
+          <t>CM-26-01124</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6733,7 +6673,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Blanc de Blancs Dosaggio Zero</t>
+          <t>Tertre Blanc</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -6743,158 +6683,158 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Alessandra Divella</t>
+          <t>Château du Tertre</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2344</v>
+        <v>822</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>26'400.15</t>
+          <t>7'004.52</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0577</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0327</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01113</t>
+          <t>CM-26-01021</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Vivaltus</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Bodega Vivaltus</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2206</v>
+        <v>2974</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>48'374.15</t>
+          <t>31'780.50</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0368</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0394</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01124</t>
+          <t>CM-26-01192</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Tertre Blanc</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite,Margaux,Haut Brion,Mission,Cheval ,Ausone,Yquem)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château du Tertre</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>822</v>
+        <v>1174</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>7'004.52</t>
+          <t>63'981.51</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0577</v>
+        <v>0.0073</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.0361</v>
       </c>
     </row>
   </sheetData>
@@ -6942,7 +6882,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10003,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (April 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 27 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 28 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2277,201 +2277,201 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>135</v>
+        <v>692</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01330</t>
+          <t>CM-26-01353</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Gaia &amp; Rey Chardonnay</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>407</v>
+        <v>63</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>47'219.26</t>
+          <t>11'782.68</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.09</v>
+        <v>0.0342</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0585</v>
+        <v>0.0146</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>361</v>
+        <v>776</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01332</t>
+          <t>CM-26-01365</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bòggina Bianco</t>
+          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1792</v>
+        <v>496</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>22'161.78</t>
+          <t>24'653.16</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0614</v>
+        <v>0.0174</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0305</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0478</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>692</v>
+        <v>874</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01353</t>
+          <t>CM-26-01393</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>11'782.68</t>
+          <t>897.26</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.0291</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0146</v>
+        <v>0.0011</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>776</v>
+        <v>922</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01365</t>
+          <t>CM-26-01367</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -2490,98 +2490,98 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>496</v>
+        <v>1334</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>24'653.16</t>
+          <t>8'623.53</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0174</v>
+        <v>0.0194</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0305</v>
+        <v>0.0107</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0226</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>793</v>
+        <v>959</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01342</t>
+          <t>CM-26-01364</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>481</v>
+        <v>898</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>5'734.85</t>
+          <t>4'314.05</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0314</v>
+        <v>0.0192</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0071</v>
+        <v>0.0053</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0217</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>870</v>
+        <v>995</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01333</t>
+          <t>CM-26-01391</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2591,326 +2591,326 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>584</v>
+        <v>5857</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>5'486.90</t>
+          <t>16'965.76</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0043</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.021</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0182</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>874</v>
+        <v>1172</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01393</t>
+          <t>CM-26-01345</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Prosecco Brut Millesimato</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Pontet Canet</t>
+          <t>Villa Marcello</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>74</v>
+        <v>806</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>897.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>922</v>
+        <v>1173</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01367</t>
+          <t>CM-26-01351</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Minuty 281 Rosé</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Minuty</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1334</v>
+        <v>149</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>8'623.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0194</v>
+        <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0107</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>959</v>
+        <v>1174</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01364</t>
+          <t>CM-26-01352</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Minuty 281 Rosé</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Minuty</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>898</v>
+        <v>80</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>4'314.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0053</v>
+        <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>995</v>
+        <v>1175</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01391</t>
+          <t>CM-26-01360</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Axelle de Valandraud</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Pontet Canet</t>
+          <t>Château Valandraud</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5857</v>
+        <v>2174</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>16'965.76</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01345</t>
+          <t>CM-26-01379</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Prosecco Brut Millesimato</t>
+          <t>Champagne Brut Belle Epoque</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Villa Marcello</t>
+          <t>Perrier-Jouët</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>806</v>
+        <v>1301</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
@@ -2937,40 +2937,32 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01351</t>
+          <t>CM-26-01381</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Case Basse - Gianfranco Soldera</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>149</v>
+        <v>5312</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0</v>
@@ -2997,11 +2989,11 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01352</t>
+          <t>CM-26-01383</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -3011,26 +3003,26 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Château Palmer</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -3057,40 +3049,32 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01360</t>
+          <t>CM-26-01396</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Axelle de Valandraud</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Château Valandraud</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2174</v>
+        <v>833</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3115,232 +3099,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>1176</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01379</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Champagne Brut Belle Epoque</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Perrier-Jouët</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1301</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>1177</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01381</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>5312</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1178</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01383</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Château Palmer</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>460</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1179</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01396</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>833</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N22"/>
+  <autoFilter ref="A3:N18"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3377,14 +3137,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 20 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 21 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -3642,21 +3402,21 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01256</t>
+          <t>CM-26-01330</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Gaia &amp; Rey Chardonnay</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3666,187 +3426,187 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Spottswoode</t>
+          <t>Gaja</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3420</v>
+        <v>407</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>130'884.01</t>
+          <t>47'219.26</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0396</v>
+        <v>0.09</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1622</v>
+        <v>0.0585</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0886</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01330</t>
+          <t>CM-26-01302</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Gaia &amp; Rey Chardonnay</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>407</v>
+        <v>777</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>47'219.26</t>
+          <t>117'808.49</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0194</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0585</v>
+        <v>0.146</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01302</t>
+          <t>CM-26-01282</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Champagne Brut Cristal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Louis Roederer</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>777</v>
+        <v>2546</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>117'808.49</t>
+          <t>84'326.26</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0194</v>
+        <v>0.0347</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.146</v>
+        <v>0.1045</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0626</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>225</v>
+        <v>330</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01282</t>
+          <t>CM-26-01289</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Cristal</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Louis Roederer</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3855,98 +3615,98 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2546</v>
+        <v>868</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'326.26</t>
+          <t>81'799.39</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0174</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1045</v>
+        <v>0.1013</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0626</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01289</t>
+          <t>CM-26-01306</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Family and Friends</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Feudo Maccari</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>868</v>
+        <v>2492</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>81'799.39</t>
+          <t>27'067.91</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0597</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1013</v>
+        <v>0.0335</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.051</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01306</t>
+          <t>CM-26-01332</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -3956,127 +3716,127 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Family and Friends</t>
+          <t>Bòggina Bianco</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Feudo Maccari</t>
+          <t>Fattoria Petrolo</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2492</v>
+        <v>1792</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>27'067.91</t>
+          <t>22'161.78</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0597</v>
+        <v>0.0614</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0335</v>
+        <v>0.0275</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>356</v>
+        <v>461</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01263</t>
+          <t>CM-26-01305</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Stella Solare</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Croix de Labrie</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1115</v>
+        <v>2198</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>15'707.45</t>
+          <t>35'344.45</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0392</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0438</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>361</v>
+        <v>523</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01332</t>
+          <t>CM-26-01297</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Bòggina Bianco</t>
+          <t>Oreno</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4086,347 +3846,347 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Tenuta Sette Ponti</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1792</v>
+        <v>2359</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>22'161.78</t>
+          <t>25'111.44</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0614</v>
+        <v>0.0403</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0311</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0478</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>461</v>
+        <v>546</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01305</t>
+          <t>CM-26-01318</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Único Reserva Especial Venta 2026 (2011+2012+2014)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Bodegas Vega Sicilia</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2198</v>
+        <v>1736</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>35'344.45</t>
+          <t>44'810.48</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0211</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.0555</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.041</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>523</v>
+        <v>596</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01297</t>
+          <t>CM-26-01321</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Oreno</t>
+          <t>Champagne Brut 7 Crus</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Tenuta Sette Ponti</t>
+          <t>Agrapart &amp; Fils</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2359</v>
+        <v>1065</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>25'111.44</t>
+          <t>10'605.80</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0403</v>
+        <v>0.0446</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0311</v>
+        <v>0.0131</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0366</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>546</v>
+        <v>692</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01318</t>
+          <t>CM-26-01353</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Único Reserva Especial Venta 2026 (2011+2012+2014)</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Vega Sicilia</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1736</v>
+        <v>63</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>44'810.48</t>
+          <t>11'782.68</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0342</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0555</v>
+        <v>0.0146</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>596</v>
+        <v>744</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01321</t>
+          <t>CM-26-01275</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut 7 Crus</t>
+          <t>Brunello di Montalcino</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Agrapart &amp; Fils</t>
+          <t>Biondi Santi</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1065</v>
+        <v>2693</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>10'605.80</t>
+          <t>34'153.87</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.0121</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0131</v>
+        <v>0.0423</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>644</v>
+        <v>746</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01247</t>
+          <t>CM-26-01304</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Baronarques Blanc</t>
+          <t>Belvedere</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Baronarques</t>
+          <t>Castello Luigi</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2960</v>
+        <v>3071</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>14'141.51</t>
+          <t>19'883.46</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0239</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0175</v>
+        <v>0.0246</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0292</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>692</v>
+        <v>776</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01353</t>
+          <t>CM-26-01365</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4436,117 +4196,117 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>63</v>
+        <v>496</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>11'782.68</t>
+          <t>24'653.16</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.0174</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0305</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0264</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>744</v>
+        <v>793</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01275</t>
+          <t>CM-26-01342</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino</t>
+          <t>Châteauneuf du Pape Vieilles Vignes</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Biondi Santi</t>
+          <t>Domaine de Marcoux</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2693</v>
+        <v>481</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>34'153.87</t>
+          <t>5'734.85</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0121</v>
+        <v>0.0314</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0423</v>
+        <v>0.0071</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0242</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>746</v>
+        <v>870</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01304</t>
+          <t>CM-26-01333</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4556,67 +4316,67 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Belvedere</t>
+          <t>Châteauneuf du Pape Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Castello Luigi</t>
+          <t>Domaine de Marcoux</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3071</v>
+        <v>584</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>19'883.46</t>
+          <t>5'486.90</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0239</v>
+        <v>0.0258</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0246</v>
+        <v>0.0068</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0242</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>776</v>
+        <v>874</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01365</t>
+          <t>CM-26-01393</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -4626,7 +4386,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -4635,218 +4395,218 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>496</v>
+        <v>74</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>24'653.16</t>
+          <t>897.26</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0291</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0305</v>
+        <v>0.0011</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0226</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>793</v>
+        <v>922</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01342</t>
+          <t>CM-26-01367</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>481</v>
+        <v>1334</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>5'734.85</t>
+          <t>8'623.53</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0314</v>
+        <v>0.0194</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.0107</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>870</v>
+        <v>941</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01333</t>
+          <t>CM-26-01316</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Macan</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Rothschild/Vega Sicilia</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>584</v>
+        <v>3001</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>5'486.90</t>
+          <t>10'468.00</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0258</v>
+        <v>0.0157</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0068</v>
+        <v>0.013</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0182</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>872</v>
+        <v>959</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01269</t>
+          <t>CM-26-01364</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Barbaresco Asili Riserva</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Falletto di Bruno Giacosa</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1304</v>
+        <v>898</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>24'290.88</t>
+          <t>4'314.05</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0192</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0301</v>
+        <v>0.0053</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.018</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>874</v>
+        <v>995</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01393</t>
+          <t>CM-26-01391</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -4875,38 +4635,38 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>74</v>
+        <v>5857</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>897.26</t>
+          <t>16'965.76</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.0043</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0011</v>
+        <v>0.021</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0179</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>922</v>
+        <v>1021</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01367</t>
+          <t>CM-26-01283</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4916,48 +4676,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Minuty 281 Rosé</t>
+          <t>Chevalier de Lascombes</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Minuty</t>
+          <t>Château Lascombes</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1334</v>
+        <v>2262</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>12</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>8'623.53</t>
+          <t>4'418.02</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0194</v>
+        <v>0.0114</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0107</v>
+        <v>0.0055</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0159</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4998,14 +4758,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 13 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 14 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -6463,71 +6223,71 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01206</t>
+          <t>CM-26-01321</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Beau-Séjour Bécot</t>
+          <t>Champagne Brut 7 Crus</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Beau-Séjour Bécot</t>
+          <t>Agrapart &amp; Fils</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2858</v>
+        <v>1065</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>32'961.78</t>
+          <t>10'605.80</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0446</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0408</v>
+        <v>0.0131</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0335</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>596</v>
+        <v>644</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01321</t>
+          <t>CM-26-01247</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6537,48 +6297,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut 7 Crus</t>
+          <t>Baronarques Blanc</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Agrapart &amp; Fils</t>
+          <t>Domaine de Baronarques</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1065</v>
+        <v>2960</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>10'605.80</t>
+          <t>14'141.51</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.037</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0131</v>
+        <v>0.0175</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0292</v>
       </c>
     </row>
   </sheetData>
@@ -6626,7 +6386,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9507,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (May 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 03 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 08 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2217,71 +2217,71 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>4</v>
+        <v>956</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01713</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80</v>
+        <v>703</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>22.50%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>89'655.03</t>
+          <t>17'154.02</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4704</v>
+        <v>0.0148</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.111</v>
+        <v>0.0212</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3266</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>234</v>
+        <v>1082</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2291,57 +2291,57 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1862</v>
+        <v>509</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>11'937.82</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.138</v>
+        <v>0.0148</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.0606</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>283</v>
+        <v>1179</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5146</v>
+        <v>2115</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>356.30</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.001</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1191</v>
+        <v>0.0004</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>343</v>
+        <v>1276</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2421,57 +2421,57 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3866</v>
+        <v>532</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0737</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>407</v>
+        <v>1277</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2481,47 +2481,47 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>707</v>
+        <v>418</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>10'973.28</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>580</v>
+        <v>1278</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01785</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2541,866 +2541,102 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>18'986.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0418</v>
+        <v>0</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>707</v>
+        <v>1279</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01716</t>
+          <t>CM-26-01771</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Léoville Poyferré</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Poyferré</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>605</v>
+        <v>514</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>23'090.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0276</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0286</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>722</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01715</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>439</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>15'102.94</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.0274</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>956</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01778</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Champagne Brut Grande Cuvée</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Krug</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>703</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>17'154.02</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.0174</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>1074</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01717</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1326</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>11'780.82</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0115</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>1079</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01726</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Beychevelle</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Château Beychevelle</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>881.02</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.0111</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>1082</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01789</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>509</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>11'937.82</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0108</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>1169</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01718</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>431</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2'304.18</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>1179</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01787</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>San Leonardo</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Tenuta San Leonardo</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>2115</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>356.30</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>1276</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01788</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>532</v>
-      </c>
-      <c r="I18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>1277</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01786</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>418</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>1278</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01785</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>461</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1279</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01771</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>514</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1280</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01760</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>975</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>1281</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01756</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>5248</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N23"/>
+  <autoFilter ref="A3:N10"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3437,14 +2673,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 27 May 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 01 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -3642,21 +2878,21 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01641</t>
+          <t>CM-26-01695</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3666,57 +2902,57 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Trotanoy</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>51</v>
+        <v>495</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>17.65%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>17'219.32</t>
+          <t>21'418.67</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.369</v>
+        <v>0.1606</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0265</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2299</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01698</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3726,47 +2962,47 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>495</v>
+        <v>3950</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>21'418.67</t>
+          <t>141'031.82</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1606</v>
+        <v>0.0222</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0265</v>
+        <v>0.1746</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.107</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01701</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3776,7 +3012,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Reserve de la Comtesse (2nd Vin)</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3786,7 +3022,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Pichon-Longueville Comtesse de Lalande</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -3795,38 +3031,38 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3950</v>
+        <v>3667</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>141'031.82</t>
+          <t>121'427.44</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0291</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.1503</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0832</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01697</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3836,7 +3072,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -3846,7 +3082,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Pavie</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -3855,48 +3091,48 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3667</v>
+        <v>2842</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>121'427.44</t>
+          <t>89'670.37</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.028</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1503</v>
+        <v>0.111</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0776</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01679</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>La Mission Haut-Brion</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3906,47 +3142,47 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2342</v>
+        <v>1862</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>138'853.14</t>
+          <t>111'433.62</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1719</v>
+        <v>0.138</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01646</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3956,67 +3192,67 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Éphémère 030</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Drémont &amp; Savart</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>938</v>
+        <v>4119</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>20'179.93</t>
+          <t>67'692.38</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0891</v>
+        <v>0.0391</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0838</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0635</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4026,107 +3262,107 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2842</v>
+        <v>5146</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>89'670.37</t>
+          <t>96'159.60</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.028</v>
+        <v>0.0142</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.111</v>
+        <v>0.1191</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0612</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1862</v>
+        <v>1480</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>24'790.36</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.138</v>
+        <v>0.0307</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0606</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4151,52 +3387,52 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4119</v>
+        <v>3866</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>67'692.38</t>
+          <t>59'543.87</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0351</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0838</v>
+        <v>0.0737</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.057</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>283</v>
+        <v>407</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -4206,7 +3442,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -4215,288 +3451,288 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>5146</v>
+        <v>707</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>10'973.28</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.065</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1191</v>
+        <v>0.0136</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>304</v>
+        <v>560</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01704</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Sloan Red</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1480</v>
+        <v>332</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>24'790.36</t>
+          <t>26'070.11</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0707</v>
+        <v>0.0378</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0307</v>
+        <v>0.0323</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0547</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>341</v>
+        <v>580</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01676</t>
+          <t>CM-26-01714</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Corton-Charlemagne</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Rapet Père &amp; Fils</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1923</v>
+        <v>401</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>60'048.98</t>
+          <t>18'986.65</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0347</v>
+        <v>0.0418</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0743</v>
+        <v>0.0235</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>343</v>
+        <v>707</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01716</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Léoville Poyferré</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Léoville Poyferré</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3866</v>
+        <v>605</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>23'090.54</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0351</v>
+        <v>0.0276</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0737</v>
+        <v>0.0286</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>356</v>
+        <v>713</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01674</t>
+          <t>CM-26-01699</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Family and Friends Firraru</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Screaming Eagle Winery</t>
+          <t>Feudo Maccari</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>558</v>
+        <v>898</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>75'668.55</t>
+          <t>5'313.11</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0188</v>
+        <v>0.0418</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0488</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>407</v>
+        <v>722</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01715</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4506,287 +3742,287 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>707</v>
+        <v>439</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>10'973.28</t>
+          <t>15'102.94</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.065</v>
+        <v>0.0332</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0136</v>
+        <v>0.0187</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>480</v>
+        <v>851</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01639</t>
+          <t>CM-26-01694</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Palmer</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2498</v>
+        <v>238</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>71'984.09</t>
+          <t>11'589.97</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0263</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0891</v>
+        <v>0.0144</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0407</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>481</v>
+        <v>881</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01647</t>
+          <t>CM-26-01683</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Giscours</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Château Giscours</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>257</v>
+        <v>2609</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>3'284.98</t>
+          <t>12'874.12</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.065</v>
+        <v>0.0232</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0041</v>
+        <v>0.0159</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0406</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>506</v>
+        <v>912</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01652</t>
+          <t>CM-26-01685</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Galatrona</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3049</v>
+        <v>2221</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>40'374.07</t>
+          <t>13'547.97</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0316</v>
+        <v>0.0207</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.05</v>
+        <v>0.0168</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.039</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>560</v>
+        <v>956</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>332</v>
+        <v>703</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>26'070.11</t>
+          <t>17'154.02</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0378</v>
+        <v>0.0148</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0323</v>
+        <v>0.0212</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0356</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>580</v>
+        <v>1005</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01684</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -4796,57 +4032,57 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne Brut Cristal Rosé</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Louis Roederer</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>401</v>
+        <v>769</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>18'986.65</t>
+          <t>14'036.89</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.0136</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0235</v>
+        <v>0.0174</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0345</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>630</v>
+        <v>1009</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01648</t>
+          <t>CM-26-01710</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4856,168 +4092,168 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Champagne Brut R Vintage</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Maison Ruinart</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>846</v>
+        <v>1276</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>10'872.49</t>
+          <t>6'347.58</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0445</v>
+        <v>0.0197</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0135</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0321</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>691</v>
+        <v>1074</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01658</t>
+          <t>CM-26-01717</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Bourgogne Côte d'Or "Cuvée de Pressonnier"</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Joseph Roty</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1433</v>
+        <v>1326</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>8'774.83</t>
+          <t>11'780.82</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0408</v>
+        <v>0.0094</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0109</v>
+        <v>0.0146</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0288</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>706</v>
+        <v>1079</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01659</t>
+          <t>CM-26-01726</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Riesling 1G Westhofener</t>
+          <t>Beychevelle</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Weingut Wittmann</t>
+          <t>Château Beychevelle</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>419</v>
+        <v>118</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2'263.65</t>
+          <t>881.02</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0178</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0028</v>
+        <v>0.0011</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0281</v>
+        <v>0.0111</v>
       </c>
     </row>
   </sheetData>
@@ -5058,14 +4294,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 20 May 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 25 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -5323,21 +4559,21 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01577</t>
+          <t>CM-26-01695</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Carillon de l'Angélus (2nd Vin)</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -5347,47 +4583,47 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Angélus</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3203</v>
+        <v>495</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>237'861.60</t>
+          <t>21'418.67</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.028</v>
+        <v>0.1606</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2945</v>
+        <v>0.0265</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1346</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01635</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5397,297 +4633,297 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Le Serre Nuove dell'Ornellaia</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Tenuta dell'Ornellaia</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>495</v>
+        <v>283</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>6.71%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>21'418.67</t>
+          <t>7'981.81</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1606</v>
+        <v>0.1403</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.107</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01567</t>
+          <t>CM-26-01698</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>203</v>
+        <v>3950</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>23'081.35</t>
+          <t>141'031.82</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1545</v>
+        <v>0.0222</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.1746</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1041</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01635</t>
+          <t>CM-26-01701</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Le Serre Nuove dell'Ornellaia</t>
+          <t>Reserve de la Comtesse (2nd Vin)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Tenuta dell'Ornellaia</t>
+          <t>Château Pichon-Longueville Comtesse de Lalande</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>283</v>
+        <v>3667</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>7'981.81</t>
+          <t>121'427.44</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1403</v>
+        <v>0.0291</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.1503</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0881</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01564</t>
+          <t>CM-26-01679</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>La Mission Haut-Brion</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2628</v>
+        <v>2342</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>85'987.35</t>
+          <t>138'853.14</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0142</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1065</v>
+        <v>0.1719</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01646</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Champagne Extra Brut Éphémère 030</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Drémont &amp; Savart</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3950</v>
+        <v>938</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>141'031.82</t>
+          <t>20'179.93</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.0891</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.025</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0832</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01697</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5697,7 +4933,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -5707,7 +4943,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Pavie</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -5716,48 +4952,48 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3667</v>
+        <v>2842</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>121'427.44</t>
+          <t>89'670.37</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.028</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1503</v>
+        <v>0.111</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0776</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>136</v>
+        <v>234</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01679</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>La Mission Haut-Brion</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5767,57 +5003,57 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2342</v>
+        <v>1862</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>138'853.14</t>
+          <t>111'433.62</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1719</v>
+        <v>0.138</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01575</t>
+          <t>CM-26-01624</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Les Ormes de Pez</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -5827,47 +5063,47 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Les Ormes de Pez</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3188</v>
+        <v>52</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>83'446.96</t>
+          <t>20'164.81</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0491</v>
+        <v>0.0805</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1033</v>
+        <v>0.025</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0708</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01646</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -5877,67 +5113,67 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Éphémère 030</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Drémont &amp; Savart</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>938</v>
+        <v>4119</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>20'179.93</t>
+          <t>67'692.38</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0891</v>
+        <v>0.0391</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0838</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -5947,167 +5183,167 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2842</v>
+        <v>5146</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>89'670.37</t>
+          <t>96'159.60</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.028</v>
+        <v>0.0142</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.111</v>
+        <v>0.1191</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1862</v>
+        <v>1480</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>24'790.36</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0307</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>254</v>
+        <v>341</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01624</t>
+          <t>CM-26-01676</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Corton-Charlemagne</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine Rapet Père &amp; Fils</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>52</v>
+        <v>1923</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>20'164.81</t>
+          <t>60'048.98</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0805</v>
+        <v>0.0347</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0743</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0583</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6132,292 +5368,292 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4119</v>
+        <v>3866</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>67'692.38</t>
+          <t>59'543.87</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0351</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0838</v>
+        <v>0.0737</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.057</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01633</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Ducru Beaucaillou</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Château Ducru Beaucaillou</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>5146</v>
+        <v>1055</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>41'812.62</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0475</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1191</v>
+        <v>0.0518</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>285</v>
+        <v>356</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01590</t>
+          <t>CM-26-01674</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Palmer</t>
+          <t>Screaming Eagle Winery</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2657</v>
+        <v>558</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>80'925.55</t>
+          <t>75'668.55</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0268</v>
+        <v>0.0188</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1002</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01594</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Clos Apalta</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Lapostolle Winery</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1480</v>
+        <v>5530</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>24'790.36</t>
+          <t>64'545.20</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0707</v>
+        <v>0.0276</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0307</v>
+        <v>0.0799</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0547</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01676</t>
+          <t>CM-26-01638</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Corton-Charlemagne</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Domaine Rapet Père &amp; Fils</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1923</v>
+        <v>3870</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>60'048.98</t>
+          <t>46'484.89</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0362</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0743</v>
+        <v>0.0576</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -6427,107 +5663,107 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3866</v>
+        <v>707</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>10'973.28</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0351</v>
+        <v>0.065</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0737</v>
+        <v>0.0136</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>352</v>
+        <v>431</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01633</t>
+          <t>CM-26-01592</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Ducru Beaucaillou</t>
+          <t>Whispering Angel Rosé</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Ducru Beaucaillou</t>
+          <t>Château d'Esclans</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1055</v>
+        <v>2164</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>41'812.62</t>
+          <t>19'954.56</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0475</v>
+        <v>0.056</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0518</v>
+        <v>0.0247</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>353</v>
+        <v>480</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01615</t>
+          <t>CM-26-01639</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -6537,108 +5773,108 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Carruades de Lafite Rothschild (2nd Vin)</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Château Palmer</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2238</v>
+        <v>2498</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>72'015.06</t>
+          <t>71'984.09</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0224</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0892</v>
+        <v>0.0891</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0491</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>356</v>
+        <v>481</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01674</t>
+          <t>CM-26-01647</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Screaming Eagle Winery</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>558</v>
+        <v>257</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>75'668.55</t>
+          <t>3'284.98</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.065</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0041</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.0406</v>
       </c>
     </row>
   </sheetData>
@@ -6686,7 +5922,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9043,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:58  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (May 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 15 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 16 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2757,91 +2757,91 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>1031</v>
+        <v>1071</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01847</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Aalto</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1664</v>
+        <v>1119</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>7'074.83</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0129</v>
+        <v>0.0058</v>
       </c>
       <c r="M13" s="6" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="N13" s="6" t="n">
         <v>0.008800000000000001</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0113</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01909</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -2850,38 +2850,38 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1119</v>
+        <v>160</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>10'753.00</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0136</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.0012</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>1074</v>
+        <v>1100</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01894</t>
+          <t>CM-26-01895</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2910,48 +2910,48 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>160</v>
+        <v>3616</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>963.07</t>
+          <t>7'002.23</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0136</v>
+        <v>0.0054</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0012</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0086</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01895</t>
+          <t>CM-26-01940</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Almaviva</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2961,67 +2961,67 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3616</v>
+        <v>3416</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>7'002.23</t>
+          <t>4'668.32</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0054</v>
+        <v>0.0043</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>1115</v>
+        <v>1227</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01940</t>
+          <t>CM-26-01925</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Almaviva</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -3030,38 +3030,38 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3416</v>
+        <v>134</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>4'668.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01925</t>
+          <t>CM-26-01922</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -3086,11 +3086,11 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3117,40 +3117,32 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01922</t>
+          <t>CM-26-01884</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3177,11 +3169,11 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01884</t>
+          <t>CM-26-01880</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3202,7 +3194,7 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3229,11 +3221,11 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01880</t>
+          <t>CM-26-01879</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3254,7 +3246,7 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
@@ -3281,11 +3273,11 @@
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01879</t>
+          <t>CM-26-01877</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3306,7 +3298,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -3333,11 +3325,11 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01877</t>
+          <t>CM-26-01864</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3354,11 +3346,11 @@
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3385,11 +3377,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01864</t>
+          <t>CM-26-01863</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3410,7 +3402,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3437,11 +3429,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01863</t>
+          <t>CM-26-01859</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -3462,7 +3454,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>278</v>
+        <v>88</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3489,11 +3481,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01859</t>
+          <t>CM-26-01858</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3514,7 +3506,7 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -3541,11 +3533,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01858</t>
+          <t>CM-26-01856</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -3566,7 +3558,7 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
@@ -3591,60 +3583,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>1237</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01856</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N28"/>
+  <autoFilter ref="A3:N27"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3681,14 +3621,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 08 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 09 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -4066,131 +4006,131 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>703</v>
+        <v>2297</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0459</v>
+        <v>0.0243</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0436</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2297</v>
+        <v>1175</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0243</v>
+        <v>0.0073</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0433</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>467</v>
+        <v>558</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4200,117 +4140,117 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1175</v>
+        <v>509</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.0254</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.09</v>
+        <v>0.0482</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0404</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>558</v>
+        <v>669</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>509</v>
+        <v>940</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0276</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.0295</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>669</v>
+        <v>721</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01907</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4320,307 +4260,307 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>940</v>
+        <v>2662</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>23'816.30</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0129</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0295</v>
+        <v>0.0452</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>721</v>
+        <v>799</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01912</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2662</v>
+        <v>138</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>36'543.63</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0129</v>
+        <v>0.0155</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0452</v>
+        <v>0.0326</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01935</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>138</v>
+        <v>2115</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>26'352.00</t>
+          <t>16'195.97</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.0213</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.0201</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0223</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01787</t>
+          <t>CM-26-01825</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>San Leonardo</t>
+          <t>Cuvée Etoile Rosé</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Tenuta San Leonardo</t>
+          <t>Domaine Ott</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2115</v>
+        <v>2762</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>16'195.97</t>
+          <t>16'897.97</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0202</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0201</v>
+        <v>0.0209</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0208</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>836</v>
+        <v>870</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01825</t>
+          <t>CM-26-01893</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Cuvée Etoile Rosé</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ott</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2762</v>
+        <v>494</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'897.97</t>
+          <t>7'134.74</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.0261</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0209</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0205</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01893</t>
+          <t>CM-26-01875</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Le Difese</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4630,182 +4570,182 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Tenuta San Guido</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>494</v>
+        <v>748</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>7'134.74</t>
+          <t>1'563.78</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0261</v>
+        <v>0.0289</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01875</t>
+          <t>CM-26-01841</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Le Difese</t>
+          <t>Champagne Brut Cuvée Argonne</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Tenuta San Guido</t>
+          <t>Henri Giraud</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>748</v>
+        <v>3042</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>1'563.78</t>
+          <t>25'571.66</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0289</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0019</v>
+        <v>0.0317</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0181</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>906</v>
+        <v>951</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01841</t>
+          <t>CM-26-01913</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Cuvée Argonne</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Henri Giraud</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3042</v>
+        <v>763</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>25'571.66</t>
+          <t>11'063.16</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0317</v>
+        <v>0.0137</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0177</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01913</t>
+          <t>CM-26-01900</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -4819,38 +4759,38 @@
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>11'063.16</t>
+          <t>2'668.29</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.017</v>
+        <v>0.0215</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0137</v>
+        <v>0.0033</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>979</v>
+        <v>1031</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01900</t>
+          <t>CM-26-01847</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4860,149 +4800,149 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bourgogne Chardonnay</t>
+          <t>Aalto</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Aalto Bodegas y Viñedos</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>800</v>
+        <v>1664</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2'668.29</t>
+          <t>7'074.83</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.0129</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0033</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01847</t>
+          <t>CM-26-01837</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Aalto</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Château Ausone</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1664</v>
+        <v>1926</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>7'074.83</t>
+          <t>12'907.55</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0129</v>
+        <v>0.0067</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0113</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01837</t>
+          <t>CM-26-01801</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Ausone</t>
+          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Ausone</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1926</v>
+        <v>2540</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -5011,106 +4951,106 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>12'907.55</t>
+          <t>12'675.17</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
         <v>0.0067</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.016</v>
+        <v>0.0157</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1041</v>
+        <v>1071</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01801</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2540</v>
+        <v>1119</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'675.17</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.0058</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0157</v>
+        <v>0.0133</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0103</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01909</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -5119,149 +5059,149 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1119</v>
+        <v>160</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>10'753.00</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0136</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>1074</v>
+        <v>1096</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01894</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>160</v>
+        <v>532</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>963.07</t>
+          <t>3'842.02</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0136</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0012</v>
+        <v>0.0048</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0086</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01788</t>
+          <t>CM-26-01895</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>532</v>
+        <v>3616</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>3'842.02</t>
+          <t>7'002.23</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0054</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0048</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
     </row>
   </sheetData>
@@ -5302,14 +5242,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 01 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 02 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -5627,71 +5567,71 @@
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01842</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>495</v>
+        <v>1076</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>8.89%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>23'490.85</t>
+          <t>154'116.50</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1915</v>
+        <v>0.0321</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0291</v>
+        <v>0.1908</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1265</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01842</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5701,57 +5641,57 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1076</v>
+        <v>418</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>154'116.50</t>
+          <t>53'350.72</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.098</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1908</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0956</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01786</t>
+          <t>CM-26-01868</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -5761,67 +5701,67 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Lodovico</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Tenuta di Biserno</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>418</v>
+        <v>163</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>53'350.72</t>
+          <t>21'470.52</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.098</v>
+        <v>0.1189</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0266</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -5831,167 +5771,167 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3950</v>
+        <v>3866</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>136'772.14</t>
+          <t>77'935.68</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0485</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1693</v>
+        <v>0.0965</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0827</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01868</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>163</v>
+        <v>1480</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>21'470.52</t>
+          <t>26'612.38</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1189</v>
+        <v>0.0844</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0266</v>
+        <v>0.033</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.082</v>
+        <v>0.0638</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3667</v>
+        <v>1862</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>121'721.15</t>
+          <t>111'613.62</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0347</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1507</v>
+        <v>0.1382</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -6001,7 +5941,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6011,57 +5951,57 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3866</v>
+        <v>5146</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>77'935.68</t>
+          <t>97'063.91</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0485</v>
+        <v>0.0196</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0965</v>
+        <v>0.1202</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0677</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -6071,7 +6011,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -6080,48 +6020,48 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1480</v>
+        <v>4119</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>26'612.38</t>
+          <t>68'593.06</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0844</v>
+        <v>0.0418</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.033</v>
+        <v>0.0849</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0638</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>222</v>
+        <v>373</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6131,117 +6071,117 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2842</v>
+        <v>707</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>89'026.43</t>
+          <t>10'823.31</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.067</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1102</v>
+        <v>0.0134</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0618</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>226</v>
+        <v>385</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1862</v>
+        <v>703</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>111'613.62</t>
+          <t>35'222.13</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0459</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1382</v>
+        <v>0.0436</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0609</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>235</v>
+        <v>396</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01714</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -6251,287 +6191,287 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5146</v>
+        <v>401</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>97'063.91</t>
+          <t>25'015.66</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0536</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.031</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0598</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>247</v>
+        <v>416</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4119</v>
+        <v>2297</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>68'593.06</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.0243</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0849</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.059</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>373</v>
+        <v>467</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>707</v>
+        <v>1175</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>10'823.31</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.067</v>
+        <v>0.0073</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0134</v>
+        <v>0.09</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>385</v>
+        <v>541</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01704</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Sloan Red</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>703</v>
+        <v>332</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>24'356.51</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0459</v>
+        <v>0.039</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0436</v>
+        <v>0.0302</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>396</v>
+        <v>558</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>401</v>
+        <v>509</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>25'015.66</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0536</v>
+        <v>0.0254</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.031</v>
+        <v>0.0482</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>416</v>
+        <v>587</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01715</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -6541,67 +6481,67 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2297</v>
+        <v>439</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>18'907.18</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0243</v>
+        <v>0.0392</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0234</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0433</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>467</v>
+        <v>666</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01716</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Léoville Poyferré</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -6611,167 +6551,167 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Château Léoville Poyferré</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1175</v>
+        <v>605</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>23'090.54</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.0284</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0286</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>541</v>
+        <v>669</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>332</v>
+        <v>940</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>24'356.51</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.039</v>
+        <v>0.0276</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0302</v>
+        <v>0.0295</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>554</v>
+        <v>721</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01699</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Family and Friends Firraru</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Feudo Maccari</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>898</v>
+        <v>2662</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>6'012.58</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.0129</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0074</v>
+        <v>0.0452</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0346</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>558</v>
+        <v>799</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -6781,108 +6721,108 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>509</v>
+        <v>138</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0155</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.0326</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0345</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>587</v>
+        <v>828</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01715</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>439</v>
+        <v>2115</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>18'907.18</t>
+          <t>16'195.97</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.0213</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0234</v>
+        <v>0.0201</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0329</v>
+        <v>0.0208</v>
       </c>
     </row>
   </sheetData>
@@ -6930,7 +6870,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -10051,7 +9991,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report_filtered.xlsx
+++ b/AVUwinnersCM/winners_report_filtered.xlsx
@@ -16,8 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (May 2026)'!$A$3:$N$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Campaigns'!$A$3:$N$1282</definedName>
@@ -29,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +57,10 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00999999"/>
     </font>
   </fonts>
   <fills count="5">
@@ -109,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +135,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +530,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -2105,6 +2109,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 23 Jun 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Wine</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Vintage</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Buyers</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Conv %</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Sales (CHF)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Norm Conv</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Norm Sales</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>No data for this period.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2132,14 +2263,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 16 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 16 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -3585,1627 +3716,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:N27"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 09 Jun 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Campaign</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>💰</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Wine</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Vintage</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Producer</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Emails</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Buyers</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Conv %</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Sales (CHF)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Norm Conv</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Norm Sales</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01836</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>La Dame de Montrose (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Château Montrose</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>3643</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>196'646.81</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0.2435</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.1496</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01785</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>461</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>5.21%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>127'563.05</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.1122</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.1579</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.1305</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01842</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Margaux</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Château Margaux</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1076</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>154'116.50</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0321</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.1908</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.0956</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>113</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01786</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>418</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>4.55%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>53'350.72</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0.06610000000000001</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0.0852</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01868</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Lodovico</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Tenuta di Biserno</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>5.52%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>21'470.52</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.1189</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0.0266</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>416</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01843</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Grands Echézeaux</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Mongeard Mugneret</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>2297</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>1.13%</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>58'066.22</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.0433</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>467</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01945</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Lafite Rothschild</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Château Lafite Rothschild</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>0.34%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>72'662.43</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0.0404</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>558</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01789</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>509</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>38'932.73</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.0254</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.0482</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.0345</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>669</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01907</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Meursault Perrières</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>940</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>1.28%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>23'816.30</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.0284</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>721</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01912</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Léoville Las Cases</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Château Léoville Las Cases</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>2662</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>36'543.63</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0258</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>799</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01935</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.72%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>26'352.00</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.0223</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>828</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01787</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>San Leonardo</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Tenuta San Leonardo</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>2115</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>16'195.97</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.0213</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.0201</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0208</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>836</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01825</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Cuvée Etoile Rosé</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ott</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2762</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>16'897.97</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0.0205</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>870</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01893</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>494</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>7'134.74</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.0261</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.0192</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>895</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01875</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Le Difese</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Tenuta San Guido</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>748</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>1'563.78</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0.0181</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>906</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01841</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Champagne Brut Cuvée Argonne</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Henri Giraud</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>3042</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>25'571.66</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.0177</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>951</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01913</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Meursault Perrières</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>763</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>11'063.16</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0.0137</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0.0157</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>979</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01900</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Bourgogne Chardonnay</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>800</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>2'668.29</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0.0142</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1031</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01847</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Aalto</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Aalto Bodegas y Viñedos</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1664</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>7'074.83</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0.0113</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>1039</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01837</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Ausone</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Château Ausone</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1926</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>0.31%</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>12'907.55</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0.0104</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>1041</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01801</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Dom Pérignon</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>2540</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>0.31%</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>12'675.17</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0.0103</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>1071</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01909</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>1119</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>10'753.00</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>1074</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01894</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>963.07</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0.0086</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>1096</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01788</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>532</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>0.38%</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>3'842.02</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0.0068</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01895</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>3616</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>7'002.23</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>0.0067</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:N28"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -5242,14 +3752,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 02 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 09 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -5327,21 +3837,21 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01713</t>
+          <t>CM-26-01836</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>La Dame de Montrose (2nd Vin)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -5351,47 +3861,47 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Montrose</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80</v>
+        <v>3643</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>27.50%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>99'331.85</t>
+          <t>196'646.81</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.5923</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.123</v>
+        <v>0.2435</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4046</v>
+        <v>0.1496</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01706</t>
+          <t>CM-26-01785</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -5401,7 +3911,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -5411,107 +3921,107 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3482</v>
+        <v>461</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>461'514.36</t>
+          <t>127'563.05</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.0545</v>
+        <v>0.1122</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5714</v>
+        <v>0.1579</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.2613</v>
+        <v>0.1305</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01836</t>
+          <t>CM-26-01842</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>La Dame de Montrose (2nd Vin)</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Montrose</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3643</v>
+        <v>1076</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>196'646.81</t>
+          <t>154'116.50</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0321</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2435</v>
+        <v>0.1908</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1496</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01785</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5540,38 +4050,38 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>461</v>
+        <v>418</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>127'563.05</t>
+          <t>53'350.72</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1122</v>
+        <v>0.098</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1579</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1305</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01842</t>
+          <t>CM-26-01868</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5581,57 +4091,57 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Lodovico</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Tenuta di Biserno</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1076</v>
+        <v>163</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>154'116.50</t>
+          <t>21'470.52</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0321</v>
+        <v>0.1189</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1908</v>
+        <v>0.0266</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0956</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>113</v>
+        <v>416</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01786</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5641,357 +4151,357 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>418</v>
+        <v>2297</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>53'350.72</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.098</v>
+        <v>0.0243</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0852</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>122</v>
+        <v>467</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01868</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>163</v>
+        <v>1175</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>21'470.52</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1189</v>
+        <v>0.0073</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0266</v>
+        <v>0.09</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.082</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>179</v>
+        <v>558</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3866</v>
+        <v>509</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>77'935.68</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0485</v>
+        <v>0.0254</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0965</v>
+        <v>0.0482</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0677</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>207</v>
+        <v>669</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1480</v>
+        <v>940</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>26'612.38</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0844</v>
+        <v>0.0276</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.033</v>
+        <v>0.0295</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0638</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>226</v>
+        <v>721</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1862</v>
+        <v>2662</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>111'613.62</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0129</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1382</v>
+        <v>0.0452</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0609</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>235</v>
+        <v>799</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5146</v>
+        <v>138</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>97'063.91</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0196</v>
+        <v>0.0155</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1202</v>
+        <v>0.0326</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0598</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>247</v>
+        <v>828</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -6001,57 +4511,57 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4119</v>
+        <v>2115</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>68'593.06</t>
+          <t>16'195.97</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.0213</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0849</v>
+        <v>0.0201</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.059</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>373</v>
+        <v>836</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01825</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -6061,57 +4571,57 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Cuvée Etoile Rosé</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Domaine Ott</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>707</v>
+        <v>2762</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>10'823.31</t>
+          <t>16'897.97</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.067</v>
+        <v>0.0202</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0134</v>
+        <v>0.0209</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0456</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>385</v>
+        <v>870</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01893</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -6121,117 +4631,117 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>703</v>
+        <v>494</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>7'134.74</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0459</v>
+        <v>0.0261</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0436</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>396</v>
+        <v>895</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01875</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Le Difese</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Tenuta San Guido</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>401</v>
+        <v>748</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>10</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>25'015.66</t>
+          <t>1'563.78</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0536</v>
+        <v>0.0289</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.031</v>
+        <v>0.0019</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>416</v>
+        <v>906</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01841</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6241,17 +4751,17 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Champagne Brut Cuvée Argonne</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Henri Giraud</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -6260,58 +4770,58 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2297</v>
+        <v>3042</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>25'571.66</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0243</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0317</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0433</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>467</v>
+        <v>951</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01913</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -6320,158 +4830,158 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1175</v>
+        <v>763</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>11'063.16</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.017</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0137</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>541</v>
+        <v>979</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01900</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>332</v>
+        <v>800</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>24'356.51</t>
+          <t>2'668.29</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.039</v>
+        <v>0.0215</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0302</v>
+        <v>0.0033</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0355</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>558</v>
+        <v>1031</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01847</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Aalto</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Aalto Bodegas y Viñedos</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>509</v>
+        <v>1664</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>7'074.83</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0129</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>587</v>
+        <v>1039</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01715</t>
+          <t>CM-26-01837</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -6481,7 +4991,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -6491,47 +5001,47 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Ausone</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>439</v>
+        <v>1926</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>18'907.18</t>
+          <t>12'907.55</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0067</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0234</v>
+        <v>0.016</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0329</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>666</v>
+        <v>1041</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01716</t>
+          <t>CM-26-01801</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -6541,117 +5051,117 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Léoville Poyferré</t>
+          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Poyferré</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>605</v>
+        <v>2540</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>23'090.54</t>
+          <t>12'675.17</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0284</v>
+        <v>0.0067</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.0157</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0285</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>669</v>
+        <v>1071</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01907</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>940</v>
+        <v>1119</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>23'816.30</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0058</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0295</v>
+        <v>0.0133</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>721</v>
+        <v>1074</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01912</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6661,168 +5171,168 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2662</v>
+        <v>160</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>36'543.63</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0129</v>
+        <v>0.0136</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0452</v>
+        <v>0.0012</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>799</v>
+        <v>1096</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01935</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>138</v>
+        <v>532</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>26'352.00</t>
+          <t>3'842.02</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.0048</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0223</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>828</v>
+        <v>1100</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01787</t>
+          <t>CM-26-01895</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>San Leonardo</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Tenuta San Leonardo</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2115</v>
+        <v>3616</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>16'195.97</t>
+          <t>7'002.23</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0054</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0201</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0208</v>
+        <v>0.0067</v>
       </c>
     </row>
   </sheetData>
@@ -6870,7 +5380,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
@@ -9991,7 +8501,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt; 50</t>
         </is>
       </c>
     </row>
